--- a/data/trans_orig/P33B3_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P33B3_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Poblacion según la frecuencia con la que se despierta demasiado temprano de forma involuntaria en 2023</t>
+          <t>Poblacion según la frecuencia con la que se despierta demasiado temprano de forma involuntaria en 2023 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -735,7 +735,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4531</t>
+          <t>4334</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>836</t>
+          <t>965</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>5397</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>1368</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6859</t>
+          <t>7075</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7969</t>
+          <t>9121</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22945</t>
+          <t>24888</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18862</t>
+          <t>18708</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>33051</t>
+          <t>33133</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>31100</t>
+          <t>31638</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>51631</t>
+          <t>51832</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,62%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9703</t>
+          <t>9487</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>25195</t>
+          <t>24914</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>21287</t>
+          <t>22153</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>36812</t>
+          <t>37605</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>35123</t>
+          <t>34821</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>58051</t>
+          <t>56723</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,44%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>268057</t>
+          <t>268034</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>289456</t>
+          <t>289728</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>222417</t>
+          <t>221902</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>243876</t>
+          <t>242358</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>76,79%</t>
+          <t>76,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>84,2%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>496470</t>
+          <t>497511</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>526914</t>
+          <t>526022</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>82,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,51%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12959</t>
+          <t>13183</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>41416</t>
+          <t>39326</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>21480</t>
+          <t>21621</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>39573</t>
+          <t>39757</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>37968</t>
+          <t>38500</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>68487</t>
+          <t>69575</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,73%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22460</t>
+          <t>22674</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>50260</t>
+          <t>47285</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>36632</t>
+          <t>36672</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>58617</t>
+          <t>57848</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>66007</t>
+          <t>64807</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>98433</t>
+          <t>98283</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,51%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>59069</t>
+          <t>59815</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>98866</t>
+          <t>99152</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>86245</t>
+          <t>84357</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>115389</t>
+          <t>115277</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>155187</t>
+          <t>152702</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>202563</t>
+          <t>200810</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,43%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>360116</t>
+          <t>357993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>407737</t>
+          <t>408020</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>69,47%</t>
+          <t>69,06%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>78,65%</t>
+          <t>78,71%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>319097</t>
+          <t>321014</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>356785</t>
+          <t>357473</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>61,96%</t>
+          <t>62,34%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>69,42%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>693001</t>
+          <t>694153</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>756783</t>
+          <t>754918</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>67,06%</t>
+          <t>67,17%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>73,24%</t>
+          <t>73,05%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>20327</t>
+          <t>19770</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>37322</t>
+          <t>37129</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>25809</t>
+          <t>25747</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>42500</t>
+          <t>43583</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>49836</t>
+          <t>49663</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>74760</t>
+          <t>74213</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,17%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15710</t>
+          <t>15531</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>31890</t>
+          <t>31783</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>31209</t>
+          <t>30870</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>49127</t>
+          <t>50091</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>50938</t>
+          <t>50546</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>77237</t>
+          <t>75282</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,33%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22290</t>
+          <t>22075</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>39679</t>
+          <t>40662</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>40484</t>
+          <t>39175</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>61463</t>
+          <t>60732</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>66129</t>
+          <t>67461</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>95593</t>
+          <t>96804</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,57%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>220556</t>
+          <t>220552</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>247926</t>
+          <t>248714</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,69%</t>
+          <t>78,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>209608</t>
+          <t>210327</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>237890</t>
+          <t>240580</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>60,04%</t>
+          <t>60,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>68,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>439212</t>
+          <t>435837</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>479333</t>
+          <t>480610</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>66,13%</t>
+          <t>65,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,17%</t>
+          <t>72,36%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16855</t>
+          <t>16740</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>39432</t>
+          <t>39869</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>23097</t>
+          <t>22848</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>54346</t>
+          <t>54606</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>47097</t>
+          <t>46991</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>86406</t>
+          <t>86058</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,92%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>20023</t>
+          <t>19772</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>47014</t>
+          <t>45489</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>25261</t>
+          <t>24301</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>59094</t>
+          <t>57602</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>51496</t>
+          <t>48763</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>95353</t>
+          <t>93332</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>11,84%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>36319</t>
+          <t>36120</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>65732</t>
+          <t>65455</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>61676</t>
+          <t>56026</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>131031</t>
+          <t>131251</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>112600</t>
+          <t>108590</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>184509</t>
+          <t>182690</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>23,18%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>183443</t>
+          <t>184517</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>225551</t>
+          <t>225414</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>58,69%</t>
+          <t>59,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>72,16%</t>
+          <t>72,12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>243109</t>
+          <t>243552</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>362605</t>
+          <t>368993</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>51,1%</t>
+          <t>51,2%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>76,22%</t>
+          <t>77,57%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>450044</t>
+          <t>452328</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>579605</t>
+          <t>577155</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>57,09%</t>
+          <t>57,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>73,53%</t>
+          <t>73,22%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2293</t>
+          <t>2086</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>9284</t>
+          <t>9563</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6576</t>
+          <t>6756</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>14065</t>
+          <t>14395</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>10234</t>
+          <t>10632</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>20100</t>
+          <t>20550</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,31%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6695</t>
+          <t>6791</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>16037</t>
+          <t>15677</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>8726</t>
+          <t>9009</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>17524</t>
+          <t>18369</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>18190</t>
+          <t>17749</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>30681</t>
+          <t>30226</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,81%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>108688</t>
+          <t>107429</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>131431</t>
+          <t>130933</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>60,81%</t>
+          <t>60,1%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>73,53%</t>
+          <t>73,25%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>140912</t>
+          <t>139551</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>160019</t>
+          <t>159894</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>67,66%</t>
+          <t>67,0%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>76,83%</t>
+          <t>76,77%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>257282</t>
+          <t>256927</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>286690</t>
+          <t>285662</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>66,48%</t>
+          <t>66,39%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>74,08%</t>
+          <t>73,81%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>32011</t>
+          <t>31774</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>53962</t>
+          <t>54538</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>26302</t>
+          <t>26956</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>44554</t>
+          <t>45103</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>63238</t>
+          <t>64196</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>91324</t>
+          <t>92191</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,82%</t>
         </is>
       </c>
     </row>
@@ -3575,12 +3575,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>11575</t>
+          <t>11541</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>26087</t>
+          <t>26803</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>15419</t>
+          <t>15015</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>28490</t>
+          <t>28622</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>30854</t>
+          <t>30978</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>49715</t>
+          <t>49122</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,33%</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3688,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>19459</t>
+          <t>20048</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>36421</t>
+          <t>36323</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>36459</t>
+          <t>36064</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>53638</t>
+          <t>52529</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>60137</t>
+          <t>60636</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>85062</t>
+          <t>83735</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>15,9%</t>
         </is>
       </c>
     </row>
@@ -3801,12 +3801,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>26648</t>
+          <t>27693</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>47309</t>
+          <t>47220</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>30096</t>
+          <t>31005</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>46074</t>
+          <t>46864</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>62148</t>
+          <t>62937</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>87687</t>
+          <t>88124</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,73%</t>
         </is>
       </c>
     </row>
@@ -3914,12 +3914,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>174636</t>
+          <t>174863</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>201756</t>
+          <t>200880</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3929,12 +3929,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>64,77%</t>
+          <t>64,85%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>74,83%</t>
+          <t>74,5%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3949,12 +3949,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>139817</t>
+          <t>140865</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>165408</t>
+          <t>165847</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>54,39%</t>
+          <t>54,8%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>64,35%</t>
+          <t>64,52%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>323995</t>
+          <t>324949</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>359053</t>
+          <t>360331</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>61,52%</t>
+          <t>61,7%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>68,17%</t>
+          <t>68,41%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>39823</t>
+          <t>38897</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>73269</t>
+          <t>73947</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>33601</t>
+          <t>35730</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>103782</t>
+          <t>105821</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>82108</t>
+          <t>83526</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>158664</t>
+          <t>158041</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,73%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>44705</t>
+          <t>44709</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>78432</t>
+          <t>77961</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4277,7 +4277,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>41817</t>
+          <t>42539</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>116563</t>
+          <t>115738</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>85161</t>
+          <t>93952</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>173423</t>
+          <t>175411</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,91%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>95898</t>
+          <t>92934</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>139947</t>
+          <t>137266</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>64934</t>
+          <t>60834</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>167395</t>
+          <t>168523</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>141143</t>
+          <t>152413</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>285396</t>
+          <t>291777</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,81%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>367993</t>
+          <t>364721</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>421185</t>
+          <t>421139</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>59,04%</t>
+          <t>58,52%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>67,58%</t>
+          <t>67,57%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>472060</t>
+          <t>470157</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>688088</t>
+          <t>705024</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>55,58%</t>
+          <t>55,36%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>83,02%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>871409</t>
+          <t>863988</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1165064</t>
+          <t>1126080</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>59,18%</t>
+          <t>58,67%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>76,47%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>48526</t>
+          <t>52069</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>159958</t>
+          <t>162922</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>125024</t>
+          <t>125118</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>161660</t>
+          <t>159916</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>158284</t>
+          <t>154753</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>309944</t>
+          <t>308308</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,75%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>14432</t>
+          <t>17827</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>55612</t>
+          <t>55602</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4841,7 +4841,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>74243</t>
+          <t>73684</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>101788</t>
+          <t>100388</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>77625</t>
+          <t>81792</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>154816</t>
+          <t>153684</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,35%</t>
         </is>
       </c>
     </row>
@@ -4939,12 +4939,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>39039</t>
+          <t>35471</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>125380</t>
+          <t>125230</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>92641</t>
+          <t>90412</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>122482</t>
+          <t>121640</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>120877</t>
+          <t>123694</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>234282</t>
+          <t>237653</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,45%</t>
         </is>
       </c>
     </row>
@@ -5052,12 +5052,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>597578</t>
+          <t>595316</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>824150</t>
+          <t>820088</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5067,12 +5067,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>64,34%</t>
+          <t>64,1%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>88,3%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>357069</t>
+          <t>359861</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>404742</t>
+          <t>404617</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>49,91%</t>
+          <t>50,3%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>56,58%</t>
+          <t>56,56%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>958806</t>
+          <t>957747</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1277779</t>
+          <t>1294914</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>58,32%</t>
+          <t>58,25%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>77,72%</t>
+          <t>78,76%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>211610</t>
+          <t>202431</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>303189</t>
+          <t>305232</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>284318</t>
+          <t>289864</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>393181</t>
+          <t>393274</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>545353</t>
+          <t>534790</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>677308</t>
+          <t>679143</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,54%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>179675</t>
+          <t>187849</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>273694</t>
+          <t>271955</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>303510</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>420014</t>
+          <t>421723</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>535011</t>
+          <t>534577</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>673845</t>
+          <t>674359</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5480,7 +5480,7 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>411403</t>
+          <t>416339</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>594409</t>
+          <t>596112</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>564177</t>
+          <t>569538</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>763656</t>
+          <t>763516</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>1063379</t>
+          <t>1066915</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>1324425</t>
+          <t>1322797</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,59%</t>
         </is>
       </c>
     </row>
@@ -5621,12 +5621,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>2325331</t>
+          <t>2323094</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>2671353</t>
+          <t>2679751</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5636,12 +5636,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>67,25%</t>
+          <t>67,18%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>77,26%</t>
+          <t>77,5%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>2104171</t>
+          <t>2108351</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>2498472</t>
+          <t>2476478</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>57,5%</t>
+          <t>57,61%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>67,67%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>4490376</t>
+          <t>4490366</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>4979233</t>
+          <t>4975461</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>69,96%</t>
+          <t>69,91%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P33B3_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P33B3_2023-Provincia-trans_orig.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>838</t>
+          <t>805</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4334</t>
+          <t>4400</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,22 +760,22 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3084</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>965</t>
+          <t>1046</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5397</t>
+          <t>6635</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>3246</t>
+          <t>3889</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1368</t>
+          <t>1536</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7075</t>
+          <t>8136</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>14786</t>
+          <t>13321</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9121</t>
+          <t>7709</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24888</t>
+          <t>21051</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>25405</t>
+          <t>26098</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18708</t>
+          <t>19895</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>33133</t>
+          <t>34010</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>40192</t>
+          <t>39419</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>31638</t>
+          <t>30634</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>51832</t>
+          <t>51252</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,07%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>15636</t>
+          <t>17251</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9487</t>
+          <t>10877</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>24914</t>
+          <t>27133</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>28965</t>
+          <t>33594</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>22153</t>
+          <t>26056</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>37605</t>
+          <t>42886</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>44601</t>
+          <t>50845</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>34821</t>
+          <t>40801</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>56723</t>
+          <t>63551</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>10,01%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>280182</t>
+          <t>287469</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>268034</t>
+          <t>276455</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>289728</t>
+          <t>296958</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>86,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>232857</t>
+          <t>253285</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>221902</t>
+          <t>241917</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>242358</t>
+          <t>263826</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>80,4%</t>
+          <t>80,14%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>76,61%</t>
+          <t>76,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>83,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>513039</t>
+          <t>540753</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>497511</t>
+          <t>524364</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>526022</t>
+          <t>554491</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>85,35%</t>
+          <t>85,17%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>82,77%</t>
+          <t>82,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>87,33%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21928</t>
+          <t>22685</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13183</t>
+          <t>12813</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>39326</t>
+          <t>36400</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>29681</t>
+          <t>30170</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>21621</t>
+          <t>22253</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>39757</t>
+          <t>40463</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>51609</t>
+          <t>52855</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>38500</t>
+          <t>39615</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>69575</t>
+          <t>69554</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,46%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>33272</t>
+          <t>33578</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22674</t>
+          <t>22663</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>47285</t>
+          <t>48160</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>46802</t>
+          <t>50699</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>36672</t>
+          <t>40019</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>57848</t>
+          <t>63784</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>80075</t>
+          <t>84277</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>64807</t>
+          <t>67957</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>98283</t>
+          <t>102200</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,49%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>77803</t>
+          <t>79818</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>59815</t>
+          <t>62252</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>99152</t>
+          <t>99777</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>99438</t>
+          <t>104418</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>84357</t>
+          <t>90327</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>115277</t>
+          <t>119755</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>177241</t>
+          <t>184236</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>152702</t>
+          <t>160464</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>200810</t>
+          <t>208339</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,34%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>385387</t>
+          <t>394566</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>357993</t>
+          <t>371059</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>408020</t>
+          <t>416252</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>74,36%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>69,06%</t>
+          <t>69,93%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>78,71%</t>
+          <t>78,44%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>339047</t>
+          <t>361207</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>321014</t>
+          <t>342395</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>357473</t>
+          <t>380346</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>65,84%</t>
+          <t>66,1%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>62,34%</t>
+          <t>62,65%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>69,42%</t>
+          <t>69,6%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>724434</t>
+          <t>755773</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>694153</t>
+          <t>721926</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>754918</t>
+          <t>784358</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>70,1%</t>
+          <t>70,16%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>67,17%</t>
+          <t>67,02%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>72,82%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>27487</t>
+          <t>27167</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>19770</t>
+          <t>19106</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>37129</t>
+          <t>37528</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>33706</t>
+          <t>35125</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>25747</t>
+          <t>26752</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>43583</t>
+          <t>44699</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>61193</t>
+          <t>62293</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>49663</t>
+          <t>50758</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>74213</t>
+          <t>76304</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,37%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>22432</t>
+          <t>23661</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15531</t>
+          <t>15981</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>31783</t>
+          <t>33236</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>39429</t>
+          <t>40844</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>30870</t>
+          <t>32799</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>50091</t>
+          <t>51867</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>61861</t>
+          <t>64505</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>50546</t>
+          <t>51613</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>75282</t>
+          <t>78149</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,64%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>29965</t>
+          <t>30083</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22075</t>
+          <t>21438</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>40662</t>
+          <t>39396</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>50929</t>
+          <t>52118</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>39175</t>
+          <t>41620</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>60732</t>
+          <t>63503</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>80895</t>
+          <t>82201</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>67461</t>
+          <t>67752</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>96804</t>
+          <t>95729</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,26%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>235197</t>
+          <t>234094</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>220552</t>
+          <t>219803</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>248714</t>
+          <t>247289</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>74,65%</t>
+          <t>74,31%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,0%</t>
+          <t>69,78%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>78,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>225063</t>
+          <t>228294</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>210327</t>
+          <t>213287</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>240580</t>
+          <t>243382</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>64,46%</t>
+          <t>64,06%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>60,24%</t>
+          <t>59,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>68,91%</t>
+          <t>68,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>460260</t>
+          <t>462388</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>435837</t>
+          <t>444263</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>480610</t>
+          <t>484218</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>69,29%</t>
+          <t>68,87%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>65,62%</t>
+          <t>66,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,36%</t>
+          <t>72,12%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>315081</t>
+          <t>315006</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>315081</t>
+          <t>315006</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>315081</t>
+          <t>315006</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>664209</t>
+          <t>671387</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>664209</t>
+          <t>671387</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>664209</t>
+          <t>671387</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>26483</t>
+          <t>31808</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16740</t>
+          <t>20066</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>39869</t>
+          <t>47702</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>39733</t>
+          <t>45342</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>22848</t>
+          <t>35197</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>54606</t>
+          <t>58799</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>66216</t>
+          <t>77150</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>46991</t>
+          <t>62208</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>86058</t>
+          <t>98257</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>12,36%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>30362</t>
+          <t>33054</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>19772</t>
+          <t>21992</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>45489</t>
+          <t>53876</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>41126</t>
+          <t>45426</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>24301</t>
+          <t>33929</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>57602</t>
+          <t>60008</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>71488</t>
+          <t>78480</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>48763</t>
+          <t>62066</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>93332</t>
+          <t>100950</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>12,7%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>50266</t>
+          <t>57000</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>36120</t>
+          <t>43198</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>65455</t>
+          <t>74684</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>102276</t>
+          <t>109683</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>56026</t>
+          <t>93782</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>131251</t>
+          <t>126582</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>152542</t>
+          <t>166683</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>108590</t>
+          <t>142827</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>182690</t>
+          <t>191404</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>24,07%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>205447</t>
+          <t>251283</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>184517</t>
+          <t>227085</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>225414</t>
+          <t>273530</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>65,73%</t>
+          <t>67,34%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>59,03%</t>
+          <t>60,86%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>72,12%</t>
+          <t>73,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>292583</t>
+          <t>221510</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>243552</t>
+          <t>201497</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>368993</t>
+          <t>241756</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>61,5%</t>
+          <t>52,5%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>47,75%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>57,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>498029</t>
+          <t>472794</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>452328</t>
+          <t>442490</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>577155</t>
+          <t>502132</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>63,18%</t>
+          <t>59,46%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>57,38%</t>
+          <t>55,65%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>73,22%</t>
+          <t>63,15%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>4828</t>
+          <t>5157</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2086</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>9563</t>
+          <t>10254</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,22 +3036,22 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>9993</t>
+          <t>10825</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6756</t>
+          <t>7356</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>14395</t>
+          <t>15285</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>14821</t>
+          <t>15982</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>10632</t>
+          <t>11549</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>20550</t>
+          <t>22327</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,16%</t>
         </is>
       </c>
     </row>
@@ -3114,69 +3114,69 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>10524</t>
+          <t>11150</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6791</t>
+          <t>6953</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>15677</t>
+          <t>16825</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
+          <t>8,18%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>14227</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>9973</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>19892</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>6,27%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>4,4%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
           <t>8,77%</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>12901</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>9009</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>18369</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>6,19%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>4,33%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>8,82%</t>
-        </is>
-      </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
           <t>54</t>
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>23425</t>
+          <t>25377</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>17749</t>
+          <t>19102</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>30226</t>
+          <t>32619</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,54%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>121462</t>
+          <t>137100</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>107429</t>
+          <t>124592</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>130933</t>
+          <t>149945</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>67,95%</t>
+          <t>66,66%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>60,1%</t>
+          <t>60,58%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>73,25%</t>
+          <t>72,91%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>150372</t>
+          <t>161545</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>139551</t>
+          <t>150341</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>159894</t>
+          <t>170903</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>72,2%</t>
+          <t>71,22%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>67,0%</t>
+          <t>66,28%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>75,35%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>271834</t>
+          <t>298645</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>256927</t>
+          <t>281097</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>285662</t>
+          <t>314230</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>70,24%</t>
+          <t>69,05%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>66,39%</t>
+          <t>65,0%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>73,81%</t>
+          <t>72,66%</t>
         </is>
       </c>
     </row>
@@ -3340,32 +3340,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>41928</t>
+          <t>52258</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>31774</t>
+          <t>41319</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>54538</t>
+          <t>64676</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>35008</t>
+          <t>40227</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>26956</t>
+          <t>31005</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>45103</t>
+          <t>51701</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>76936</t>
+          <t>92484</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>64196</t>
+          <t>77390</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>92191</t>
+          <t>108991</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>25,2%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3570,32 +3570,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>18113</t>
+          <t>18229</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>11541</t>
+          <t>12628</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>26803</t>
+          <t>26809</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,32 +3605,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>21314</t>
+          <t>22336</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>15015</t>
+          <t>16147</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>28622</t>
+          <t>29530</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,32 +3640,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>39427</t>
+          <t>40565</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>30978</t>
+          <t>31537</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>49122</t>
+          <t>51093</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,56%</t>
         </is>
       </c>
     </row>
@@ -3683,32 +3683,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>26841</t>
+          <t>26265</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>20048</t>
+          <t>18647</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>36323</t>
+          <t>35065</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,32 +3718,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>44009</t>
+          <t>45807</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>36064</t>
+          <t>37265</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>52529</t>
+          <t>54266</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>70850</t>
+          <t>72071</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>60636</t>
+          <t>60467</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>83735</t>
+          <t>84481</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,81%</t>
         </is>
       </c>
     </row>
@@ -3796,32 +3796,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>35675</t>
+          <t>34724</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>27693</t>
+          <t>26698</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>47220</t>
+          <t>45384</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3831,32 +3831,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>38654</t>
+          <t>39725</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>31005</t>
+          <t>32146</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>46864</t>
+          <t>48720</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,32 +3866,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>74329</t>
+          <t>74449</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>62937</t>
+          <t>63821</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>88124</t>
+          <t>88392</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,54%</t>
         </is>
       </c>
     </row>
@@ -3909,32 +3909,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>189008</t>
+          <t>191489</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>174863</t>
+          <t>177776</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>200880</t>
+          <t>202284</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>70,1%</t>
+          <t>70,74%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>64,85%</t>
+          <t>65,67%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>74,5%</t>
+          <t>74,72%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3944,32 +3944,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>153079</t>
+          <t>155883</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>140865</t>
+          <t>143902</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>165847</t>
+          <t>167952</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>59,55%</t>
+          <t>59,1%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>54,8%</t>
+          <t>54,56%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>64,52%</t>
+          <t>63,68%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,32 +3979,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>342086</t>
+          <t>347372</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>324949</t>
+          <t>329265</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>360331</t>
+          <t>363658</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>64,95%</t>
+          <t>65,0%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>61,7%</t>
+          <t>61,61%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>68,41%</t>
+          <t>68,04%</t>
         </is>
       </c>
     </row>
@@ -4022,17 +4022,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4139,32 +4139,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>53258</t>
+          <t>59331</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>38897</t>
+          <t>45531</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>73947</t>
+          <t>78858</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4174,32 +4174,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>75840</t>
+          <t>95573</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>35730</t>
+          <t>80679</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>105821</t>
+          <t>113758</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>129098</t>
+          <t>154904</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>83526</t>
+          <t>134718</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>158041</t>
+          <t>180803</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>12,13%</t>
         </is>
       </c>
     </row>
@@ -4252,32 +4252,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>58972</t>
+          <t>71276</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>44709</t>
+          <t>55705</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>77961</t>
+          <t>93153</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,32 +4287,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>83853</t>
+          <t>99137</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>42539</t>
+          <t>82995</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>115738</t>
+          <t>116539</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>142825</t>
+          <t>170413</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>93952</t>
+          <t>147876</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>175411</t>
+          <t>195889</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>13,14%</t>
         </is>
       </c>
     </row>
@@ -4365,32 +4365,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>116012</t>
+          <t>131431</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>92934</t>
+          <t>109374</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>137266</t>
+          <t>157092</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4400,32 +4400,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>121795</t>
+          <t>144212</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>60834</t>
+          <t>125069</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>168523</t>
+          <t>163889</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,32 +4435,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>237807</t>
+          <t>275643</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>152413</t>
+          <t>245577</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>291777</t>
+          <t>306081</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>20,53%</t>
         </is>
       </c>
     </row>
@@ -4478,32 +4478,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>395007</t>
+          <t>456566</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>364721</t>
+          <t>425087</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>421139</t>
+          <t>484351</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>63,38%</t>
+          <t>63,54%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>58,52%</t>
+          <t>59,15%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>67,57%</t>
+          <t>67,4%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4513,32 +4513,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>567778</t>
+          <t>433135</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>470157</t>
+          <t>408213</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>705024</t>
+          <t>461348</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>66,86%</t>
+          <t>56,1%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>55,36%</t>
+          <t>52,87%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>83,02%</t>
+          <t>59,76%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,32 +4548,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>962784</t>
+          <t>889701</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>863988</t>
+          <t>849979</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1126080</t>
+          <t>929623</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>65,38%</t>
+          <t>59,68%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>58,67%</t>
+          <t>57,02%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>76,47%</t>
+          <t>62,36%</t>
         </is>
       </c>
     </row>
@@ -4591,17 +4591,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>623250</t>
+          <t>718605</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>623250</t>
+          <t>718605</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>623250</t>
+          <t>718605</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4626,17 +4626,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>1472514</t>
+          <t>1490662</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1472514</t>
+          <t>1490662</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1472514</t>
+          <t>1490662</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4708,32 +4708,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>113038</t>
+          <t>127170</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>52069</t>
+          <t>107143</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>162922</t>
+          <t>146858</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4743,32 +4743,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>141539</t>
+          <t>157998</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>125118</t>
+          <t>140874</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>159916</t>
+          <t>176300</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4778,32 +4778,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>254576</t>
+          <t>285168</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>154753</t>
+          <t>259596</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>308308</t>
+          <t>314441</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>19,31%</t>
         </is>
       </c>
     </row>
@@ -4821,32 +4821,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>37168</t>
+          <t>40776</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>17827</t>
+          <t>30668</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>55602</t>
+          <t>54049</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4856,32 +4856,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>86758</t>
+          <t>99411</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>73684</t>
+          <t>81383</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>100388</t>
+          <t>114266</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4891,32 +4891,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>123926</t>
+          <t>140187</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>81792</t>
+          <t>119163</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>153684</t>
+          <t>161634</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,92%</t>
         </is>
       </c>
     </row>
@@ -4934,32 +4934,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>86593</t>
+          <t>99071</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>35471</t>
+          <t>80767</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>125230</t>
+          <t>118236</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4969,32 +4969,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>106132</t>
+          <t>122870</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>90412</t>
+          <t>105581</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>121640</t>
+          <t>140591</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5004,32 +5004,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>192725</t>
+          <t>221941</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>123694</t>
+          <t>199950</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>237653</t>
+          <t>251807</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>15,46%</t>
         </is>
       </c>
     </row>
@@ -5047,32 +5047,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>691921</t>
+          <t>531055</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>595316</t>
+          <t>503079</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>820088</t>
+          <t>557234</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>74,5%</t>
+          <t>66,54%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>64,1%</t>
+          <t>63,04%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>69,82%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5082,32 +5082,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>380963</t>
+          <t>450330</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>359861</t>
+          <t>427933</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>404617</t>
+          <t>479055</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>53,25%</t>
+          <t>54,22%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>50,3%</t>
+          <t>51,52%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>56,56%</t>
+          <t>57,68%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5117,32 +5117,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>1072884</t>
+          <t>981385</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>957747</t>
+          <t>939880</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1294914</t>
+          <t>1019648</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>65,26%</t>
+          <t>60,26%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>58,25%</t>
+          <t>57,71%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>78,76%</t>
+          <t>62,61%</t>
         </is>
       </c>
     </row>
@@ -5160,17 +5160,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5195,17 +5195,17 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5230,17 +5230,17 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>1644112</t>
+          <t>1628681</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1644112</t>
+          <t>1628681</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>1644112</t>
+          <t>1628681</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5277,32 +5277,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>265973</t>
+          <t>292352</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>202431</t>
+          <t>260031</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>305232</t>
+          <t>327369</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5312,32 +5312,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>354214</t>
+          <t>400453</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>289864</t>
+          <t>369211</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>393274</t>
+          <t>430684</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5347,32 +5347,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>620187</t>
+          <t>692806</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>534790</t>
+          <t>652314</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>679143</t>
+          <t>741865</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>10,21%</t>
         </is>
       </c>
     </row>
@@ -5390,32 +5390,32 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>234357</t>
+          <t>253081</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>187849</t>
+          <t>222458</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>271955</t>
+          <t>286683</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5425,32 +5425,32 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>380283</t>
+          <t>421648</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>316061</t>
+          <t>392528</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>421723</t>
+          <t>460424</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5460,32 +5460,32 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>614640</t>
+          <t>674729</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>534577</t>
+          <t>629565</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>674359</t>
+          <t>723269</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,96%</t>
         </is>
       </c>
     </row>
@@ -5503,32 +5503,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>533412</t>
+          <t>586479</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>416339</t>
+          <t>537915</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>596112</t>
+          <t>632500</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5538,32 +5538,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>698561</t>
+          <t>768165</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>569538</t>
+          <t>726975</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>763516</t>
+          <t>809251</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5573,32 +5573,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>1231973</t>
+          <t>1354644</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>1066915</t>
+          <t>1295799</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>1322797</t>
+          <t>1420784</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>19,56%</t>
         </is>
       </c>
     </row>
@@ -5616,32 +5616,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>2424076</t>
+          <t>2398780</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>2323094</t>
+          <t>2334855</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>2679751</t>
+          <t>2457467</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>70,1%</t>
+          <t>67,94%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>67,18%</t>
+          <t>66,13%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>77,5%</t>
+          <t>69,6%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5651,32 +5651,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>2226377</t>
+          <t>2143871</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>2108351</t>
+          <t>2087037</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>2476478</t>
+          <t>2194718</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>60,84%</t>
+          <t>57,41%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>57,61%</t>
+          <t>55,89%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>67,67%</t>
+          <t>58,77%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5686,32 +5686,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>4650453</t>
+          <t>4542651</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>4490366</t>
+          <t>4457001</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>4975461</t>
+          <t>4618111</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>65,34%</t>
+          <t>62,53%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>63,09%</t>
+          <t>61,35%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>69,91%</t>
+          <t>63,57%</t>
         </is>
       </c>
     </row>
@@ -5729,17 +5729,17 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>3457818</t>
+          <t>3530692</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>3457818</t>
+          <t>3530692</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>3457818</t>
+          <t>3530692</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5764,17 +5764,17 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>3659435</t>
+          <t>3734137</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>3659435</t>
+          <t>3734137</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>3659435</t>
+          <t>3734137</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5799,17 +5799,17 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>7117253</t>
+          <t>7264830</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>7117253</t>
+          <t>7264830</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>7117253</t>
+          <t>7264830</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
